--- a/hanmi/dist/20261025_韓美半導體模型_v0.1.xlsx
+++ b/hanmi/dist/20261025_韓美半導體模型_v0.1.xlsx
@@ -2814,7 +2814,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -2833,7 +2833,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3407,7 +3407,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -3426,7 +3426,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3862,7 +3862,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -3881,7 +3881,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4545,7 +4545,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -4564,7 +4564,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4707,7 +4707,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -4726,7 +4726,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4791,7 +4791,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -4810,7 +4810,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4875,7 +4875,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -4894,7 +4894,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4959,7 +4959,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -4978,7 +4978,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5043,7 +5043,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5062,7 +5062,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5130,7 +5130,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5149,7 +5149,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5244,7 +5244,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5263,7 +5263,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5328,7 +5328,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5347,7 +5347,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5412,7 +5412,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5431,7 +5431,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5496,7 +5496,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5515,7 +5515,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5580,7 +5580,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5599,7 +5599,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5959,7 +5959,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -5978,7 +5978,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6310,7 +6310,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -6329,7 +6329,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6431,7 +6431,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -6450,7 +6450,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6552,7 +6552,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -6571,7 +6571,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6673,7 +6673,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -6692,7 +6692,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6794,7 +6794,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261023_Disco</t>
+      <t xml:space="preserve">disco/dist/20261025_Disco</t>
     </r>
     <r>
       <rPr>
@@ -6813,7 +6813,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.3.xlsx</t>
+      <t xml:space="preserve">_v0.1.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7160,7 +7160,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -7179,7 +7179,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7369,7 +7369,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -7388,7 +7388,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7472,7 +7472,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -7491,7 +7491,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7575,7 +7575,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -7594,7 +7594,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7678,7 +7678,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261023_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
     </r>
     <r>
       <rPr>
@@ -7697,7 +7697,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.1.xlsx</t>
+      <t xml:space="preserve">_v0.4.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7771,7 +7771,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261023_</t>
+      <t xml:space="preserve">samsung/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7790,7 +7790,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7864,7 +7864,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261023_</t>
+      <t xml:space="preserve">samsung/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7883,7 +7883,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7957,7 +7957,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261023_</t>
+      <t xml:space="preserve">samsung/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -7976,7 +7976,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8050,7 +8050,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261023_</t>
+      <t xml:space="preserve">samsung/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8069,7 +8069,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8143,7 +8143,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261023_</t>
+      <t xml:space="preserve">samsung/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8162,7 +8162,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8236,7 +8236,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261023_</t>
+      <t xml:space="preserve">micron/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8255,7 +8255,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8329,7 +8329,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261023_</t>
+      <t xml:space="preserve">micron/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8348,7 +8348,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8422,7 +8422,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261023_</t>
+      <t xml:space="preserve">micron/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8441,7 +8441,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8515,7 +8515,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261023_</t>
+      <t xml:space="preserve">micron/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8534,7 +8534,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8608,7 +8608,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261023_</t>
+      <t xml:space="preserve">micron/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -8627,7 +8627,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">_v0.3.2.xlsx</t>
     </r>
     <r>
       <rPr>
